--- a/dataset_t6_grouped/results2/G5/G5_T6588_W0053F0001T0006Z000C1N31_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6588_W0053F0001T0006Z000C1N31_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>11.06169567069674</v>
+        <v>1.797525546488221</v>
       </c>
       <c r="D2" t="n">
-        <v>11.44309592918125</v>
+        <v>1.859503088491953</v>
       </c>
       <c r="E2" t="n">
-        <v>3.961178865335274</v>
+        <v>0.643691565616982</v>
       </c>
       <c r="F2" t="n">
-        <v>3.874104031099667</v>
+        <v>0.6295419050536959</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>3.139337940026198</v>
+        <v>0.5101424152542571</v>
       </c>
       <c r="D3" t="n">
-        <v>3.694887866981913</v>
+        <v>0.600419278384561</v>
       </c>
       <c r="E3" t="n">
-        <v>3.961178865335274</v>
+        <v>0.643691565616982</v>
       </c>
       <c r="F3" t="n">
-        <v>3.874104031099667</v>
+        <v>0.6295419050536959</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
